--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362478</v>
+        <v>131362469</v>
       </c>
       <c r="B2" t="n">
-        <v>75224</v>
+        <v>99021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528928</v>
+        <v>528893</v>
       </c>
       <c r="R2" t="n">
-        <v>6366647</v>
+        <v>6366731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362469</v>
+        <v>131362481</v>
       </c>
       <c r="B3" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +801,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528893</v>
+        <v>528960</v>
       </c>
       <c r="R3" t="n">
-        <v>6366731</v>
+        <v>6366602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362481</v>
+        <v>131362478</v>
       </c>
       <c r="B4" t="n">
-        <v>99019</v>
+        <v>75226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528960</v>
+        <v>528928</v>
       </c>
       <c r="R4" t="n">
-        <v>6366602</v>
+        <v>6366647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +952,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131362473</v>
       </c>
       <c r="B11" t="n">
-        <v>97887</v>
+        <v>97889</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131362461</v>
       </c>
       <c r="B12" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106140</v>
+        <v>106142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99019</v>
+        <v>99021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75224</v>
+        <v>75226</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362469</v>
+        <v>131362478</v>
       </c>
       <c r="B2" t="n">
-        <v>99021</v>
+        <v>75227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528893</v>
+        <v>528928</v>
       </c>
       <c r="R2" t="n">
-        <v>6366731</v>
+        <v>6366647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362481</v>
+        <v>131362469</v>
       </c>
       <c r="B3" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528960</v>
+        <v>528893</v>
       </c>
       <c r="R3" t="n">
-        <v>6366602</v>
+        <v>6366731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362478</v>
+        <v>131362481</v>
       </c>
       <c r="B4" t="n">
-        <v>75226</v>
+        <v>99022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528928</v>
+        <v>528960</v>
       </c>
       <c r="R4" t="n">
-        <v>6366647</v>
+        <v>6366602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +952,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -960,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131362473</v>
       </c>
       <c r="B11" t="n">
-        <v>97889</v>
+        <v>97890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131362461</v>
       </c>
       <c r="B12" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106142</v>
+        <v>106143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99021</v>
+        <v>99022</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75226</v>
+        <v>75227</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Tommy Carlström</t>
+          <t>Tommy Carlström, Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362478</v>
+        <v>131362469</v>
       </c>
       <c r="B2" t="n">
-        <v>75227</v>
+        <v>99022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528928</v>
+        <v>528893</v>
       </c>
       <c r="R2" t="n">
-        <v>6366647</v>
+        <v>6366731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362469</v>
+        <v>131362481</v>
       </c>
       <c r="B3" t="n">
         <v>99022</v>
@@ -806,16 +801,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528893</v>
+        <v>528960</v>
       </c>
       <c r="R3" t="n">
-        <v>6366731</v>
+        <v>6366602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362481</v>
+        <v>131362478</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>75227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528960</v>
+        <v>528928</v>
       </c>
       <c r="R4" t="n">
-        <v>6366602</v>
+        <v>6366647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +952,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131362484</v>
+        <v>131362471</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1109,7 +1109,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528991</v>
+        <v>528911</v>
       </c>
       <c r="R6" t="n">
-        <v>6366592</v>
+        <v>6366739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>grov klibbal som är ett höghus av spillkråkehål</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131362471</v>
+        <v>131362484</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1216,7 +1216,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528911</v>
+        <v>528991</v>
       </c>
       <c r="R7" t="n">
-        <v>6366739</v>
+        <v>6366592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>grov klibbal som är ett höghus av spillkråkehål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131362473</v>
+        <v>131362461</v>
       </c>
       <c r="B11" t="n">
-        <v>97890</v>
+        <v>99022</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528898</v>
+        <v>528953</v>
       </c>
       <c r="R11" t="n">
-        <v>6366754</v>
+        <v>6366580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131362461</v>
+        <v>131362473</v>
       </c>
       <c r="B12" t="n">
-        <v>99022</v>
+        <v>97890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528953</v>
+        <v>528898</v>
       </c>
       <c r="R12" t="n">
-        <v>6366580</v>
+        <v>6366754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362469</v>
+        <v>131362478</v>
       </c>
       <c r="B2" t="n">
-        <v>99022</v>
+        <v>75228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528893</v>
+        <v>528928</v>
       </c>
       <c r="R2" t="n">
-        <v>6366731</v>
+        <v>6366647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362481</v>
+        <v>131362469</v>
       </c>
       <c r="B3" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528960</v>
+        <v>528893</v>
       </c>
       <c r="R3" t="n">
-        <v>6366602</v>
+        <v>6366731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362478</v>
+        <v>131362481</v>
       </c>
       <c r="B4" t="n">
-        <v>75227</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528928</v>
+        <v>528960</v>
       </c>
       <c r="R4" t="n">
-        <v>6366647</v>
+        <v>6366602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +952,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -960,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131362471</v>
+        <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528911</v>
+        <v>528991</v>
       </c>
       <c r="R6" t="n">
-        <v>6366739</v>
+        <v>6366592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>grov klibbal som är ett höghus av spillkråkehål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131362484</v>
+        <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528991</v>
+        <v>528911</v>
       </c>
       <c r="R7" t="n">
-        <v>6366592</v>
+        <v>6366739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>grov klibbal som är ett höghus av spillkråkehål</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131362461</v>
       </c>
       <c r="B11" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131362473</v>
       </c>
       <c r="B12" t="n">
-        <v>97890</v>
+        <v>97891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106143</v>
+        <v>106144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75227</v>
+        <v>75228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,45 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362478</v>
+        <v>131362481</v>
       </c>
       <c r="B2" t="n">
-        <v>75228</v>
+        <v>99026</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528928</v>
+        <v>528960</v>
       </c>
       <c r="R2" t="n">
-        <v>6366647</v>
+        <v>6366602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,6 +753,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -756,11 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,7 +785,7 @@
         <v>131362469</v>
       </c>
       <c r="B3" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362481</v>
+        <v>131362478</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>75231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528960</v>
+        <v>528928</v>
       </c>
       <c r="R4" t="n">
-        <v>6366602</v>
+        <v>6366647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +952,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131362461</v>
+        <v>131362473</v>
       </c>
       <c r="B11" t="n">
-        <v>99023</v>
+        <v>97894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528953</v>
+        <v>528898</v>
       </c>
       <c r="R11" t="n">
-        <v>6366580</v>
+        <v>6366754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131362473</v>
+        <v>131362461</v>
       </c>
       <c r="B12" t="n">
-        <v>97891</v>
+        <v>99026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528898</v>
+        <v>528953</v>
       </c>
       <c r="R12" t="n">
-        <v>6366754</v>
+        <v>6366580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106144</v>
+        <v>106148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75228</v>
+        <v>75231</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362481</v>
+        <v>131362478</v>
       </c>
       <c r="B2" t="n">
-        <v>99026</v>
+        <v>75232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528960</v>
+        <v>528928</v>
       </c>
       <c r="R2" t="n">
-        <v>6366602</v>
+        <v>6366647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +748,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -766,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -785,7 +780,7 @@
         <v>131362469</v>
       </c>
       <c r="B3" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362478</v>
+        <v>131362481</v>
       </c>
       <c r="B4" t="n">
-        <v>75231</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528928</v>
+        <v>528960</v>
       </c>
       <c r="R4" t="n">
-        <v>6366647</v>
+        <v>6366602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +952,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -960,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131362473</v>
+        <v>131362461</v>
       </c>
       <c r="B11" t="n">
-        <v>97894</v>
+        <v>99027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528898</v>
+        <v>528953</v>
       </c>
       <c r="R11" t="n">
-        <v>6366754</v>
+        <v>6366580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131362461</v>
+        <v>131362473</v>
       </c>
       <c r="B12" t="n">
-        <v>99026</v>
+        <v>97895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528953</v>
+        <v>528898</v>
       </c>
       <c r="R12" t="n">
-        <v>6366580</v>
+        <v>6366754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106148</v>
+        <v>106153</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75231</v>
+        <v>75232</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362478</v>
+        <v>131362469</v>
       </c>
       <c r="B2" t="n">
-        <v>75232</v>
+        <v>99033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528928</v>
+        <v>528893</v>
       </c>
       <c r="R2" t="n">
-        <v>6366647</v>
+        <v>6366731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362469</v>
+        <v>131362481</v>
       </c>
       <c r="B3" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +801,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528893</v>
+        <v>528960</v>
       </c>
       <c r="R3" t="n">
-        <v>6366731</v>
+        <v>6366602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362481</v>
+        <v>131362478</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>75238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528960</v>
+        <v>528928</v>
       </c>
       <c r="R4" t="n">
-        <v>6366602</v>
+        <v>6366647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +952,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131362461</v>
+        <v>131362473</v>
       </c>
       <c r="B11" t="n">
-        <v>99027</v>
+        <v>97901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528953</v>
+        <v>528898</v>
       </c>
       <c r="R11" t="n">
-        <v>6366580</v>
+        <v>6366754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131362473</v>
+        <v>131362461</v>
       </c>
       <c r="B12" t="n">
-        <v>97895</v>
+        <v>99033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528898</v>
+        <v>528953</v>
       </c>
       <c r="R12" t="n">
-        <v>6366754</v>
+        <v>6366580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106153</v>
+        <v>106159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75232</v>
+        <v>75238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362469</v>
+        <v>131362478</v>
       </c>
       <c r="B2" t="n">
-        <v>99033</v>
+        <v>75238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528893</v>
+        <v>528928</v>
       </c>
       <c r="R2" t="n">
-        <v>6366731</v>
+        <v>6366647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362481</v>
+        <v>131362469</v>
       </c>
       <c r="B3" t="n">
         <v>99033</v>
@@ -801,21 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528960</v>
+        <v>528893</v>
       </c>
       <c r="R3" t="n">
-        <v>6366602</v>
+        <v>6366731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362478</v>
+        <v>131362481</v>
       </c>
       <c r="B4" t="n">
-        <v>75238</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528928</v>
+        <v>528960</v>
       </c>
       <c r="R4" t="n">
-        <v>6366647</v>
+        <v>6366602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +952,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -960,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131362464</v>
+        <v>131362483</v>
       </c>
       <c r="B13" t="n">
         <v>99033</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528898</v>
+        <v>528970</v>
       </c>
       <c r="R13" t="n">
-        <v>6366710</v>
+        <v>6366606</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131362483</v>
+        <v>131362464</v>
       </c>
       <c r="B14" t="n">
         <v>99033</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528970</v>
+        <v>528898</v>
       </c>
       <c r="R14" t="n">
-        <v>6366606</v>
+        <v>6366710</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131362482</v>
+        <v>131362466</v>
       </c>
       <c r="B19" t="n">
         <v>99033</v>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528962</v>
+        <v>528893</v>
       </c>
       <c r="R19" t="n">
-        <v>6366607</v>
+        <v>6366724</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131362466</v>
+        <v>131362482</v>
       </c>
       <c r="B20" t="n">
         <v>99033</v>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528893</v>
+        <v>528962</v>
       </c>
       <c r="R20" t="n">
-        <v>6366724</v>
+        <v>6366607</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362478</v>
+        <v>131362469</v>
       </c>
       <c r="B2" t="n">
-        <v>75238</v>
+        <v>99034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528928</v>
+        <v>528893</v>
       </c>
       <c r="R2" t="n">
-        <v>6366647</v>
+        <v>6366731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362469</v>
+        <v>131362481</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,16 +801,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528893</v>
+        <v>528960</v>
       </c>
       <c r="R3" t="n">
-        <v>6366731</v>
+        <v>6366602</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362481</v>
+        <v>131362478</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>75238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528960</v>
+        <v>528928</v>
       </c>
       <c r="R4" t="n">
-        <v>6366602</v>
+        <v>6366647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,11 +952,6 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>rikligt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -965,6 +960,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131362484</v>
+        <v>131362471</v>
       </c>
       <c r="B6" t="n">
         <v>57895</v>
@@ -1109,7 +1109,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528991</v>
+        <v>528911</v>
       </c>
       <c r="R6" t="n">
-        <v>6366592</v>
+        <v>6366739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>grov klibbal som är ett höghus av spillkråkehål</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131362471</v>
+        <v>131362484</v>
       </c>
       <c r="B7" t="n">
         <v>57895</v>
@@ -1216,7 +1216,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528911</v>
+        <v>528991</v>
       </c>
       <c r="R7" t="n">
-        <v>6366739</v>
+        <v>6366592</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>grov klibbal som är ett höghus av spillkråkehål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131362473</v>
       </c>
       <c r="B11" t="n">
-        <v>97901</v>
+        <v>97902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131362461</v>
       </c>
       <c r="B12" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131362483</v>
+        <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528970</v>
+        <v>528898</v>
       </c>
       <c r="R13" t="n">
-        <v>6366606</v>
+        <v>6366710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131362464</v>
+        <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528898</v>
+        <v>528970</v>
       </c>
       <c r="R14" t="n">
-        <v>6366710</v>
+        <v>6366606</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2369,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131362466</v>
+        <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528893</v>
+        <v>528962</v>
       </c>
       <c r="R19" t="n">
-        <v>6366724</v>
+        <v>6366607</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2466,10 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131362482</v>
+        <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2501,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528962</v>
+        <v>528893</v>
       </c>
       <c r="R20" t="n">
-        <v>6366607</v>
+        <v>6366724</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131362469</v>
       </c>
       <c r="B2" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131362481</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>131362478</v>
       </c>
       <c r="B4" t="n">
-        <v>75238</v>
+        <v>75239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131362471</v>
+        <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528911</v>
+        <v>528991</v>
       </c>
       <c r="R6" t="n">
-        <v>6366739</v>
+        <v>6366592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>grov klibbal som är ett höghus av spillkråkehål</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131362484</v>
+        <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528991</v>
+        <v>528911</v>
       </c>
       <c r="R7" t="n">
-        <v>6366592</v>
+        <v>6366739</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>grov klibbal som är ett höghus av spillkråkehål</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131362473</v>
+        <v>131362461</v>
       </c>
       <c r="B11" t="n">
-        <v>97902</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528898</v>
+        <v>528953</v>
       </c>
       <c r="R11" t="n">
-        <v>6366754</v>
+        <v>6366580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131362461</v>
+        <v>131362473</v>
       </c>
       <c r="B12" t="n">
-        <v>99034</v>
+        <v>97903</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528953</v>
+        <v>528898</v>
       </c>
       <c r="R12" t="n">
-        <v>6366580</v>
+        <v>6366754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106160</v>
+        <v>106161</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75238</v>
+        <v>75239</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Tommy Carlström</t>
+          <t>Tommy Carlström, Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131362469</v>
+        <v>131362478</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>75242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528893</v>
+        <v>528928</v>
       </c>
       <c r="R2" t="n">
-        <v>6366731</v>
+        <v>6366647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>glasbjörk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131362481</v>
+        <v>131362469</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528960</v>
+        <v>528893</v>
       </c>
       <c r="R3" t="n">
-        <v>6366602</v>
+        <v>6366731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,45 +874,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131362478</v>
+        <v>131362481</v>
       </c>
       <c r="B4" t="n">
-        <v>75239</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Posarp, 700 m väst, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528928</v>
+        <v>528960</v>
       </c>
       <c r="R4" t="n">
-        <v>6366647</v>
+        <v>6366602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,6 +952,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -960,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>glasbjörk</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>131362462</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>131362484</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>131362471</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>131362468</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>131362467</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131362470</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>131362461</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>131362473</v>
       </c>
       <c r="B12" t="n">
-        <v>97903</v>
+        <v>97906</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>131362464</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>131362483</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131362480</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131362463</v>
       </c>
       <c r="B16" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         <v>131362474</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106161</v>
+        <v>106159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>131362482</v>
       </c>
       <c r="B19" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>131362466</v>
       </c>
       <c r="B20" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>131354026</v>
       </c>
       <c r="B21" t="n">
-        <v>75239</v>
+        <v>75242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson, Tommy Carlström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 10376-2026 artfynd.xlsx
+++ b/artfynd/A 10376-2026 artfynd.xlsx
@@ -1588,32 +1588,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131362461</v>
+        <v>131362473</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>97906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528953</v>
+        <v>528898</v>
       </c>
       <c r="R11" t="n">
-        <v>6366580</v>
+        <v>6366754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131362473</v>
+        <v>131362461</v>
       </c>
       <c r="B12" t="n">
-        <v>97906</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528898</v>
+        <v>528953</v>
       </c>
       <c r="R12" t="n">
-        <v>6366754</v>
+        <v>6366580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2275,7 +2275,7 @@
         <v>131362472</v>
       </c>
       <c r="B18" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson, Tommy Carlström</t>
+          <t>Tommy Carlström, Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
